--- a/attrition.xlsx
+++ b/attrition.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rbb9cdec7772a4b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R839c5f629d534e36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -510,6 +510,91 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>4005903638</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Monet Anthony</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>34785</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3521 S LESCHI PL APT 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98144-2638</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bmonetanthony@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(936) 446-7661</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Access</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Move</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>31.97</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>4005907510</x:t>
         </x:is>
       </x:c>
@@ -680,6 +765,91 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>4005904697</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cormac Conner</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>30891</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>4621 52 ave S</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98118</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>cormacconner@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(206) 475-7480</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMENITIES PLUS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Expired</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Expired</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>4005905193</x:t>
         </x:is>
       </x:c>
@@ -1020,12 +1190,182 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>4005901496</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SARA TELLER</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>24838</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3709 S DAWSON ST</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98118-1911</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>gwyndolyno@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(206) 498-8537</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMENITIES PLUS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Met Min Requirement</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45817</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>54.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>4005906560</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Halle Ali</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>34550</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>6509 29th Ave South</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98108</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Hayateali@outlook.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(206) 841-4030</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CHAMPIONS CLUB</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Move</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>164.43</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>4005904946</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>HECTOR ORELLANA</x:t>
+          <x:t>Hector Orellana</x:t>
         </x:is>
       </x:c>
       <x:c s="9" t="b">
@@ -1121,7 +1461,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>111 27TH AVE E</x:t>
+          <x:t>111 27th Ave E</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -2040,6 +2380,91 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>4005904742</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LAUREN RAY</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>35863</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>4724 31st Ave Unit 8</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98108</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>laurentaks@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(808) 753-5633</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CHAMPIONS CLUB</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Move</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>169.79</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>4005902915</x:t>
         </x:is>
       </x:c>
@@ -2210,6 +2635,91 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>4005905961</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOSE MARTINEZ</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>38749</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>4219 s othello street apt 531</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98118</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>martinezjosemiguel383@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(360) 712-1221</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMENITIES PLUS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Met Min Requirement</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>4005900349</x:t>
         </x:is>
       </x:c>
@@ -2295,6 +2805,91 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>4005904714</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Mattie Schneider</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>35583</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2615 25th Ave S Apt 415</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98144</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>mattieschneider2@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(217) 710-5313</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALL-ACCESS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Move out of state/region</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>59.54</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>4005902868</x:t>
         </x:is>
       </x:c>
@@ -2635,6 +3230,91 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>4005906264</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Oakar Dyer</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>36642</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>4527 Rainier Ave S S207</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98118</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Oakarpaing.26@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(206) 877-2320</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMENITIES PLUS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Move</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>4005905219</x:t>
         </x:is>
       </x:c>
@@ -2895,7 +3575,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>RUIZHI LI</x:t>
+          <x:t>Ruizhi Li</x:t>
         </x:is>
       </x:c>
       <x:c s="9" t="b">
@@ -2906,7 +3586,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>111 27TH AVE E</x:t>
+          <x:t>111 27th Ave E</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -3235,7 +3915,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>Stacy Peck</x:t>
+          <x:t>STACY PECK</x:t>
         </x:is>
       </x:c>
       <x:c s="9" t="b">
@@ -3472,6 +4152,91 @@
       </x:c>
       <x:c s="11">
         <x:v>169.79</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>40059</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERALD CITY ATHLETICS - COLUMBIA CITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>4005905238</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Tanna Dolinsky</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>30485</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3923 S Hudson St</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEATTLE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>WA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>98118</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Tannatd@gmail.com</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>(503) 719-3390</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMENITIES PLUS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Cancelled</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Move out of state/region</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>45818</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Unspecified</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3821,7 +4586,7 @@
           <x:t>Applied filters:
 Cancels is greater than 0
 Club Selector is 40059 - EMERALD CITY ATHLETICS - COLUMBIA CITY
-FullDate is on or after 06/01/2025 and is before 06/09/2025
+FullDate is on or after 06/01/2025 and is before 06/11/2025
 isDeleted is False</x:t>
         </x:is>
       </x:c>
